--- a/data/trans_orig/P21D3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>65268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112873</t>
+          <t>111912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68517</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>111678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166858</t>
+          <t>167055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91076</t>
+          <t>92037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>139044</t>
+          <t>138681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102563</t>
+          <t>101618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175654</t>
+          <t>174974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230610</t>
+          <t>230658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8638</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>1588</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8779</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>9670</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76391</t>
+          <t>77321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>113663</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66954</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218335</t>
+          <t>215761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>165763</t>
+          <t>162692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326573</t>
+          <t>321322</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92230</t>
+          <t>89781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>75232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223397</t>
+          <t>225380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167857</t>
+          <t>172776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328072</t>
+          <t>331437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2545</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57537</t>
+          <t>56058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86944</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59218</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82757</t>
+          <t>82997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>122565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160651</t>
+          <t>160433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128048</t>
+          <t>129834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157769</t>
+          <t>158768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>173242</t>
+          <t>172159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196345</t>
+          <t>197229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>309505</t>
+          <t>309957</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347380</t>
+          <t>348222</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3874</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>25975</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152798</t>
+          <t>155279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87047</t>
+          <t>86724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64064</t>
+          <t>66007</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220495</t>
+          <t>219442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>371213</t>
+          <t>366945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>499255</t>
+          <t>499752</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229078</t>
+          <t>229654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254038</t>
+          <t>254083</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616036</t>
+          <t>618314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>780022</t>
+          <t>776779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,47 +2811,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57216</t>
+          <t>58851</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178590</t>
+          <t>178707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>201702</t>
+          <t>201400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190815</t>
+          <t>191496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206144</t>
+          <t>206390</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>375566</t>
+          <t>376020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402823</t>
+          <t>401870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1641</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>3789</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26962</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>128014</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>141663</t>
+          <t>141933</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>155787</t>
+          <t>155518</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>168178</t>
+          <t>168473</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>288219</t>
+          <t>286693</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>306794</t>
+          <t>306731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>101062</t>
+          <t>101282</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>111391</t>
+          <t>111148</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>152770</t>
+          <t>152064</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>163217</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>257831</t>
+          <t>257362</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>272222</t>
+          <t>271386</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,67 +4385,67 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>1685</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>517</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4483,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>560</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2821</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>243724</t>
+          <t>246203</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>490215</t>
+          <t>489607</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>307737</t>
+          <t>312466</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>562220</t>
+          <t>566321</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>623792</t>
+          <t>631918</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>945364</t>
+          <t>941522</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1164868</t>
+          <t>1165206</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1415592</t>
+          <t>1412086</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1010506</t>
+          <t>1011825</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1267577</t>
+          <t>1264713</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2292420</t>
+          <t>2297786</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2613632</t>
+          <t>2608184</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>106422</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>81587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111912</t>
+          <t>130062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>77783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>139554</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111678</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167055</t>
+          <t>197747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>116091</t>
+          <t>104359</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92037</t>
+          <t>80719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138681</t>
+          <t>129194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87062</t>
+          <t>101292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70189</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>116703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>203152</t>
+          <t>205651</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174974</t>
+          <t>174784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230658</t>
+          <t>233295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>105879</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77321</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113663</t>
+          <t>127264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>123623</t>
+          <t>63136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>49899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215761</t>
+          <t>79505</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>218063</t>
+          <t>169015</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162692</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>321322</t>
+          <t>193508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108920</t>
+          <t>119574</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>99410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>140139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166913</t>
+          <t>186555</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>170208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225380</t>
+          <t>199840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>275834</t>
+          <t>306129</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172776</t>
+          <t>281569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331437</t>
+          <t>329781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>69977</t>
+          <t>89353</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56058</t>
+          <t>74196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>103903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>79499</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>65724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82997</t>
+          <t>92148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>140942</t>
+          <t>168852</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122565</t>
+          <t>147133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160433</t>
+          <t>189680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>144822</t>
+          <t>162375</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129834</t>
+          <t>147976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>158768</t>
+          <t>178055</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>184784</t>
+          <t>215125</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>172159</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>197229</t>
+          <t>228996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>329606</t>
+          <t>377500</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>356934</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348222</t>
+          <t>398638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>790</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>85960</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>71424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155279</t>
+          <t>103627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>80848</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62314</t>
+          <t>68800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86724</t>
+          <t>94903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>150800</t>
+          <t>166807</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>146666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219442</t>
+          <t>187189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>447282</t>
+          <t>229106</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>366945</t>
+          <t>211488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>499752</t>
+          <t>243576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242472</t>
+          <t>260554</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229654</t>
+          <t>246613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254083</t>
+          <t>272352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>689754</t>
+          <t>489660</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618314</t>
+          <t>468821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>776779</t>
+          <t>509665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44540</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>63611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>69732</t>
+          <t>80072</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58851</t>
+          <t>66582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83875</t>
+          <t>95443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>190626</t>
+          <t>202933</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178707</t>
+          <t>190159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>201400</t>
+          <t>215394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>199569</t>
+          <t>222542</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>191496</t>
+          <t>213954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206390</t>
+          <t>230012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>390195</t>
+          <t>425475</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376020</t>
+          <t>410159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>401870</t>
+          <t>440395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,17 +3570,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>43324</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>135671</t>
+          <t>151075</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128014</t>
+          <t>143096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>141933</t>
+          <t>157957</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>162677</t>
+          <t>174971</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>155518</t>
+          <t>167346</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>168473</t>
+          <t>181324</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>298348</t>
+          <t>326046</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>286693</t>
+          <t>315782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>306731</t>
+          <t>336090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,22 +3866,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>107044</t>
+          <t>117279</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>101282</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>111148</t>
+          <t>122056</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>158369</t>
+          <t>173286</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>152064</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>162868</t>
+          <t>178122</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>265414</t>
+          <t>290565</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>257362</t>
+          <t>281601</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271386</t>
+          <t>297839</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>405056</t>
+          <t>473086</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>429964</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>489607</t>
+          <t>518785</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>375123</t>
+          <t>344416</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>312466</t>
+          <t>312930</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>566321</t>
+          <t>375775</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>780179</t>
+          <t>817503</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>631918</t>
+          <t>766603</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>941522</t>
+          <t>869858</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1250455</t>
+          <t>1086701</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1165206</t>
+          <t>1041293</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1412086</t>
+          <t>1129936</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1201847</t>
+          <t>1334324</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1011825</t>
+          <t>1302634</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1264713</t>
+          <t>1366730</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2452303</t>
+          <t>2421025</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2297786</t>
+          <t>2367854</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2608184</t>
+          <t>2473655</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,17 +5087,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,22 +5117,22 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
